--- a/www/download/COUNTRY.MLT.rpO1.xlsx
+++ b/www/download/COUNTRY.MLT.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.821684755536959</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.839100636076563</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.898078280441284</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.904384898541739</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.929851826238597</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.01871863654664</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.04756224641374</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.00792264839678</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.877192137997102</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.802021683764487</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.804162377075274</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.793408381912368</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.724495030641948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.679660773115357</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.716576242819136</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1.63678837524516</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1.57775612314792</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.49322303977444</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>1.45770182380635</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>1.54682715504669</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>1.50569040569659</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>1.43783396699781</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1.47340075946385</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>2.27524575211545</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>1.60245689500991</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1.60848525847223</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>1.57955577567188</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>1.57281301179332</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>1.52635201670177</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>1.50119910903309</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>3.30169446328992</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>3.21815264563152</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>3.10472898793577</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>3.06498848570569</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>3.17275489759823</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>3.08648195034501</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>3.02014400491933</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>3.06823597619699</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>4.6330035979314</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>3.20502068103571</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>3.28512846126454</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>3.1816882813706</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.15607849028391</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>3.00899489990929</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>2.99585064589974</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>272.138</t>
+          <t>4.17194076795801</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>273.341</t>
+          <t>4.0344805652623</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>274.43</t>
+          <t>3.85620243000618</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>278.239</t>
+          <t>3.7775279781559</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>282.002</t>
+          <t>3.96628842922066</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>285.185</t>
+          <t>3.88967311378555</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>244.532</t>
+          <t>3.77003563977038</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>288.899</t>
+          <t>3.85570483584832</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>277.161</t>
+          <t>3.31084124416792</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>3.96458954930843</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>286.041</t>
+          <t>4.04155691123138</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>287.987</t>
+          <t>3.98398675832106</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>300.123</t>
+          <t>3.84417571014814</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>306.883</t>
+          <t>3.68478835107927</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>307.78</t>
+          <t>3.6604503255125</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>239.98</t>
+          <t>169708954786.404</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>241.04</t>
+          <t>151538089281.315</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>242.001</t>
+          <t>146904893423.557</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>245.359</t>
+          <t>180638999592.801</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>248.678</t>
+          <t>203995758474.796</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>251.485</t>
+          <t>243113737161.229</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>216.96</t>
+          <t>230664009246.658</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>256.499</t>
+          <t>242732279254.713</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>245.286</t>
+          <t>271298210037.93</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>250.577</t>
+          <t>246092748110.287</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>252.301</t>
+          <t>223009405788.694</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>253.898</t>
+          <t>208791286833.404</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>264.56</t>
+          <t>175268633457.321</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>271.437</t>
+          <t>161881755668.58</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>264.649</t>
+          <t>133917565023.159</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>28995288288.0907</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>27615690722.4796</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>27553634477.2155</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>32184004611.8371</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>34882650140.662</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>37780261289.0325</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>42423162828.298</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>44646281878.3603</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>50513126212.0568</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>47381063010.1589</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>43231548821.4027</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>39506403150.8566</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>33845300640.6042</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>31994432867.1032</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>29301066490.9404</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>1022584390.00666</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>957377919.201873</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>964174764.607173</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>1088243568.29701</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>1215067511.82915</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>1363707286.64763</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>1354560539.99714</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>1332920195.39522</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>1277509145.28072</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>1055986198.20119</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>873412172.716069</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>794560423.87922</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>586588939.534849</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>502418278.061527</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>507428540.433449</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>3561.3187949198</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>3801.43526999835</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>3776.57486183372</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>4085.871506591</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>4190.90540539559</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>4038.18539125037</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>4273.94396265231</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>4798.16977936129</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>5674.44262185373</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>6229.63125339152</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>6379.3022237218</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>6659.64872455855</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>7506.92509221523</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>10335.1172703343</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>9362.29039042824</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7629.55160046804</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7652.02719661031</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7262.23696659852</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>8103.95200641658</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>8530.79712289475</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>8964.26511972902</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>8042.42383722026</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>8848.50239240012</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>10391.4379700989</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>11329.2618545472</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>11492.2244505966</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>12480.7948523151</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>13971.8519711275</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>17193.1120088509</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>14807.8475778236</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>935.033766716748</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>962.436088886035</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>878.112097574302</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>988.361789538299</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>1028.45972006696</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>1079.4579623307</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>862.927322251072</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>857.643554506389</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>1092.12927592513</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>1192.83169298121</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>1235.83258064407</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>1428.20462482944</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>1649.43198151582</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>1868.92749049352</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>1817.72581885165</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.821684755536959</t>
+          <t>236766.319941538</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.839100636076563</t>
+          <t>224508.651663486</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.898078280441284</t>
+          <t>223114.838861542</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.904384898541739</t>
+          <t>257042.137009904</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.929851826238597</t>
+          <t>274877.15437328</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.01871863654664</t>
+          <t>294387.659530799</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.04756224641374</t>
+          <t>321941.318552076</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00792264839678</t>
+          <t>332302.421468724</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.877192137997102</t>
+          <t>379046.094297895</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.802021683764487</t>
+          <t>360848.091219573</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.804162377075274</t>
+          <t>324761.435899866</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.793408381912368</t>
+          <t>290616.94101904</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.724495030641948</t>
+          <t>241307.703703726</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679660773115357</t>
+          <t>222951.87565114</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716576242819136</t>
+          <t>202786.026627114</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>8659487547.25393</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>7812339823.41196</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>6787008657.20168</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>8165760076.69435</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>8378397922.18722</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>17963940636.9223</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>7421738117.97457</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>10749187733.5331</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>7099867080.17004</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>8966456217.20122</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>11984415590.3912</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>13034909340.2922</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>15865617100.1317</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1436182189.06707</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5187372485.26665</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-288491768.419783</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-1248553816.11638</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-3365189498.63644</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-4150692945.58028</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-6597969687.33031</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-408170792.651115</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-6073405118.06963</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-7125115891.78782</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-9629760946.70845</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-7550255156.45855</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-3760118825.15963</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-2569587355.29834</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-434023842.335387</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-14732055697.7674</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-10051055586.3602</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>8947979315.67371</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9060893639.52834</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10152198155.8381</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12316453022.2746</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14976367609.5175</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>18372111429.5734</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>13495143236.0442</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>17874303625.3209</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16729628026.8785</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16516711373.6598</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15744534415.5509</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>15604496695.5905</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>16299640942.467</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>16168237886.8344</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>15238428071.6269</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1061299.734811</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>976496.533706227</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>945399.687460279</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1083295.91793434</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1194926.67722729</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1254667.29073186</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1335167.66501837</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1397707.83193546</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1639014.22791616</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1515100.35648024</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1372822.78909334</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1203898.30393711</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>977416.661851655</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>880605.282508208</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>784098.83471849</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1078796.11627176</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1032821.86172009</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1051049.17509844</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1229989.94847356</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1343558.01966637</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1470993.45435557</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1617036.95566354</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1672810.69870809</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1920003.12066028</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1865245.42558985</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1692516.91117968</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1527085.73453761</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1275249.52416799</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1174210.79563341</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1093261.55549325</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>163.68</t>
+          <t>2183.75432366237</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>157.78</t>
+          <t>2112.65111979316</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>149.32</t>
+          <t>2044.26726001742</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>145.77</t>
+          <t>2297.17374123947</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>154.68</t>
+          <t>2486.67624060495</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>150.57</t>
+          <t>2847.25664877912</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>143.78</t>
+          <t>2432.65066122194</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>147.34</t>
+          <t>2722.81729745513</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>227.52</t>
+          <t>3059.03083731146</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>160.25</t>
+          <t>3345.33148452363</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>160.85</t>
+          <t>3577.48983631473</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>157.96</t>
+          <t>4339.13982305009</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>157.28</t>
+          <t>5320.73796135974</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>152.64</t>
+          <t>5961.29617365826</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>150.12</t>
+          <t>4978.86495064032</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>330.17</t>
+          <t>60574154172.3654</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>321.82</t>
+          <t>51707093256.071</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>310.47</t>
+          <t>51790594314.2757</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>306.5</t>
+          <t>66057066151.8271</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>317.28</t>
+          <t>79345265970.1707</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>308.65</t>
+          <t>98060680151.1205</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>302.01</t>
+          <t>91627160149.7014</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>306.82</t>
+          <t>97927895484.6518</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>463.3</t>
+          <t>106338337205.469</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>320.5</t>
+          <t>95306226365.6619</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>328.51</t>
+          <t>86642729296.355</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>318.17</t>
+          <t>86859989179.0462</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>73988530167.6155</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>300.9</t>
+          <t>69732195224.8421</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>299.59</t>
+          <t>53825621551.7209</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>417.19</t>
+          <t>3077.55815565765</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>403.45</t>
+          <t>2989.78848671855</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>385.62</t>
+          <t>2760.72266341456</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>377.75</t>
+          <t>2924.43956971278</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>396.63</t>
+          <t>3136.08578646415</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>388.97</t>
+          <t>3538.13613509204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>2954.38987457375</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>385.57</t>
+          <t>3079.71544903443</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>331.08</t>
+          <t>3638.92937598667</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>396.46</t>
+          <t>4078.39464551972</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>404.16</t>
+          <t>4367.58618560208</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>398.4</t>
+          <t>5158.88821386639</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>384.42</t>
+          <t>6223.19467713802</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>368.48</t>
+          <t>6853.35799509956</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>366.05</t>
+          <t>5595.79028406079</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>149817.214</t>
+          <t>101854750134.448</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>144066.526</t>
+          <t>88065688430.252</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>147193.39</t>
+          <t>82461101421.9416</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>174643.391</t>
+          <t>97746113585.2096</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>193349.069</t>
+          <t>113945000568.778</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>214077.454</t>
+          <t>147462014924.417</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>240160.226</t>
+          <t>124578912002.567</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>253138.825</t>
+          <t>125513836489.172</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>289116.253</t>
+          <t>139206906888.25</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>277583.268</t>
+          <t>130992473537.097</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>255434.075</t>
+          <t>124229277566.099</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>235463.512</t>
+          <t>122541276571.152</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>202907.325</t>
+          <t>108210654745.363</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>192382.472</t>
+          <t>84580151422.854</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>177618.228</t>
+          <t>68139675335.8707</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>129970.731</t>
+          <t>-893.803831995282</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>120113.974</t>
+          <t>-877.137366925392</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>116752.42</t>
+          <t>-716.455403397146</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>135638.465</t>
+          <t>-627.265828473319</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>151639.409</t>
+          <t>-649.409545859193</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>161017.816</t>
+          <t>-690.879486312916</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>175939.005</t>
+          <t>-521.739213351805</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>187788.153</t>
+          <t>-356.898151579299</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>218421.279</t>
+          <t>-579.898538675215</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>198939.851</t>
+          <t>-733.063160996098</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>182747.238</t>
+          <t>-790.096349287349</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>163657.671</t>
+          <t>-819.748390816298</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>137090.363</t>
+          <t>-902.456715778277</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>126370.171</t>
+          <t>-892.061821441303</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>113296.426</t>
+          <t>-616.925333420476</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>169708.955</t>
+          <t>-41280595962.0825</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>151538.089</t>
+          <t>-36358595174.181</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>146904.893</t>
+          <t>-30670507107.6659</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>180639</t>
+          <t>-31689047433.3825</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>203995.758</t>
+          <t>-34599734598.6076</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>243113.737</t>
+          <t>-49401334773.2967</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>230664.009</t>
+          <t>-32951751852.8654</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>242732.279</t>
+          <t>-27585941004.5206</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>271298.21</t>
+          <t>-32868569682.7813</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>246092.748</t>
+          <t>-35686247171.4353</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>223009.406</t>
+          <t>-37586548269.7435</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>208791.287</t>
+          <t>-35681287392.1057</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>175268.633</t>
+          <t>-34222124577.7474</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>161881.756</t>
+          <t>-14847956198.0119</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>133917.565</t>
+          <t>-14314053784.1498</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1385.82335</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1423.35312</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1377.26698</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1476.38768</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1473.61581</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1515.93832</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1418.21509</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1626.93416</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1868.283</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1984.44397</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2041.98878</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2193.14696</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2538.99753</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>2825.1127</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>2576.19549</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>79216.672</t>
+          <t>0.0408082018147764</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>75282.304</t>
+          <t>0.0376896455875792</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>76394.826</t>
+          <t>0.0495962516759357</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>91075.039</t>
+          <t>0.0447526145337143</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>100216.535</t>
+          <t>0.0405197614288493</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>109516.879</t>
+          <t>0.0421049528694169</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>122580.589</t>
+          <t>0.0469073191731178</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>131623.481</t>
+          <t>0.0580598351060868</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>148147.555</t>
+          <t>0.0485127775549195</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>135319.237</t>
+          <t>0.0429817634714068</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>123791.909</t>
+          <t>0.0518902133423115</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>111409.301</t>
+          <t>0.0427299673264274</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>94169.943</t>
+          <t>0.051520688176504</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>97310.302</t>
+          <t>0.0377331288637923</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>84669.641</t>
+          <t>0.0303310725219007</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1616.02247943738</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1715.50960720146</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1667.34448396809</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1754.22786698853</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1785.88735535493</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1708.42222994882</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1795.89572328168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1963.83622744647</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2341.0084328578</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2657.18545419359</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2726.00838892361</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2910.50556607688</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3330.69237946551</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>4211.27127438239</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3969.63156938789</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>28995.288</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>27615.691</t>
+          <t>1951.70874750034</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27553.634</t>
+          <t>1896.64032042978</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>32184.005</t>
+          <t>1995.10864087904</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>34882.65</t>
+          <t>2031.06693944933</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>37780.261</t>
+          <t>1942.8079854763</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>42423.163</t>
+          <t>2027.75751254768</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>44646.282</t>
+          <t>2217.01603428793</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>50513.126</t>
+          <t>2649.87773934298</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>47381.063</t>
+          <t>3024.69870145227</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>43231.549</t>
+          <t>3105.22631611993</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>39506.403</t>
+          <t>3318.28575340782</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>33845.301</t>
+          <t>3798.83718075924</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>31994.433</t>
+          <t>4801.04665285912</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>29301.066</t>
+          <t>4526.25911690874</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>10387.5856369219</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>10472.6167481845</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>9483.38162869941</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>10201.0690177384</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>10220.2398503971</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>10254.1775437209</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>10625.9934267763</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>11585.0704704321</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>13726.6270515646</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>15507.6288577581</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>15925.640501504</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>17769.8778930057</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>21012.7662506392</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>24984.4029645788</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>24997.3651176415</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1022.584</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>957.378</t>
+          <t>1971.81963499446</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>964.175</t>
+          <t>2014.16080919266</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1088.244</t>
+          <t>2105.0491934226</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1215.068</t>
+          <t>2187.32487864978</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1363.707</t>
+          <t>2220.06132249716</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1354.561</t>
+          <t>2341.96233993632</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1332.92</t>
+          <t>2416.85037926708</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1277.509</t>
+          <t>2406.06824787509</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1055.986</t>
+          <t>2461.64909418327</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>873.412</t>
+          <t>2512.31847011829</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>794.56</t>
+          <t>2574.27894368699</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>586.589</t>
+          <t>2626.41985086363</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>502.418</t>
+          <t>3048.45170473549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>507.429</t>
+          <t>2961.89450481308</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1616.02247943738</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1733.12184215755</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1770.48890676647</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1850.65172602171</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1922.98613329567</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1951.74472640863</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2073.73783740309</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2140.18170002683</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2124.94077630928</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2160.56270123431</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2203.17336956751</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2255.01404420631</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2299.23424464493</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2670.20692419726</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2593.97155767355</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1358.93245775653</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1357.14530249966</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1348.45227957022</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1444.88629912096</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1442.58140055067</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1511.2096245237</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1361.36418745232</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1530.27083571207</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1758.04608065702</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1859.37692854773</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2062.21746388007</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2187.51092659218</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2732.02415924076</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2811.66718714088</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2575.92271309126</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>129970731388.305</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>120113973633.518</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>116752420215.85</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>135638464667.137</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>151639408958.882</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>161017816270.566</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>175939005005.319</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>187788152648.341</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>218421278582.07</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>198939850878.752</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>182747238031.433</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>163657671095.148</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>137090363315.219</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>126370170743.532</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>113296426157.617</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>149817213735.506</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>144066526448.639</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>147193390057.884</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>174643391025.492</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>193349069345.177</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>214077453968.013</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>240160226278.626</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>253138825484.748</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>289116253199.535</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>277583268150.303</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>255434075369.334</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>235463512360.116</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>202907325334.163</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>192382472034.895</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>177618227570.444</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>79216672485.6987</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>75282303962.1885</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>76394825745.2168</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>91075038552.9108</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>100216534815.412</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>109516879376.548</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>122580588846.667</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>131623481030.617</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>148147554814.033</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>135319237435.184</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>123791908552.99</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>111409300730.641</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>94169942903.6294</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>97310302399.0712</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>84669640576.4967</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>138874.446687167</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>139488.262001645</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>140044.246782362</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>141987.657087953</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>143908.239551269</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>145532.567350409</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>148518.699858705</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>151325.446256559</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>150581.137128626</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>148818.629624851</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>150919.65916683</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>154191.416391832</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>159111.861238722</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>163839.80861896</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>162466.36194054</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>122463.736798588</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>123005.017926314</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>123495.302319692</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>125209.060997641</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>126902.689385716</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>128335.071345203</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>131772.967257186</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>134354.368171712</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>133263.808734455</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>131304.73504799</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>133117.864507571</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>135939.780428245</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>140257.853856829</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>143503.761848436</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>144492.532243455</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>272137948.345955</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>273340778.991406</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>274430285.096707</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>278238586.090692</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>282002153.713565</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>285185181.586899</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>244531553.853267</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>288899268.348295</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>277160855.202434</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>284000169.133413</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>286041214.56216</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>287986878.933645</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>300122877.824299</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>306882575.853023</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>307779660.295915</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>239979570.570101</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>241040263.441192</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>242001023.264924</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>245359299.619592</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>248678128.718725</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>251485020.101561</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>216960210.868469</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>256499350.402692</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>245286440.92271</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>250577276.888324</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>252301097.510267</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>253897875.799843</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>264559728.038222</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>271436883.391728</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>264648734.990132</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0785096043442988</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0783260088229312</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0725635829408859</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0671800623138325</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0688251783923756</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0699078324120806</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0692388796418979</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0724385050920685</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0880048178129122</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0921735966508009</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0974095903387319</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.101508629331494</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.105364824723641</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.115065358467651</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.120196730948339</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.149374382655247</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.155770502716519</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.148432965518307</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.141043625728438</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.152727722560584</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.156792418524991</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.163142546644421</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.162375411188584</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.16653267978683</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.175757286429952</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.179013652283156</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.187159780642293</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.182028895279162</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.18440883981998</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.202179913289584</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.772116013000455</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.76590348846055</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.779003451540807</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.79177631195773</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.77844709904704</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.773299749062929</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.767618573713681</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.765186083719348</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.745462502400258</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.732069116919247</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.723576757378112</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.711331590026213</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.712606279997197</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.700525801712369</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.677623355762077</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>6810.28788</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6759.79225</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>6504.52899</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>7022.21424</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>7201.39947</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>7612.00423</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7085.95531</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7660.96435</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>9137.04683</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>10679.72391</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>11410.39724</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>12906.4076</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>15298.69514</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>17266.45712</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>16001.56341</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3197.71274</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3308.85405</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3245.0926</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3439.99494</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3473.64834</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3454.01761</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3389.1217</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3747.28687</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4407.92382</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4884.07563</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5167.44378</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5505.79668</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6530.86134</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>7612.71384</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7102.18183</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8540.10449177539</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8906.54079634492</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>9298.47153182451</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>9715.44255502075</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>10129.7218552802</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>10575.0429322389</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10878.9484176219</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>11000.1283463253</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>11266.8232314971</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>11529.1787391199</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>11932.1325426299</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>12320.7451710381</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>12719.6954845692</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>12822.9626287163</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>12793.4869850017</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
